--- a/src-tauri/tests/fixtures/e2e_expected_output.xlsx
+++ b/src-tauri/tests/fixtures/e2e_expected_output.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="分组结果" sheetId="1" r:id="rId1"/>
     <sheet name="统计结果" sheetId="2" r:id="rId2"/>
-    <sheet name="汇总信息" sheetId="3" r:id="rId3"/>
+    <sheet name="事后比较" sheetId="3" r:id="rId3"/>
+    <sheet name="汇总信息" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="335">
   <si>
     <t>kg</t>
   </si>
@@ -946,6 +947,21 @@
   </si>
   <si>
     <t>Welch ANOVA + Dunnett's T3</t>
+  </si>
+  <si>
+    <t>比较对</t>
+  </si>
+  <si>
+    <t>事后比较 P 值</t>
+  </si>
+  <si>
+    <t>组1 vs. 组2</t>
+  </si>
+  <si>
+    <t>组1 vs. 组3</t>
+  </si>
+  <si>
+    <t>组2 vs. 组3</t>
   </si>
   <si>
     <t>数据集信息</t>
@@ -4382,7 +4398,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0.96178765398946</v>
+        <v>0.9617876539894599</v>
       </c>
       <c r="C5">
         <v>0.8454506773093755</v>
@@ -4419,7 +4435,7 @@
         <v>0.657465422737867</v>
       </c>
       <c r="C7">
-        <v>0.9155757959796288</v>
+        <v>0.9155757959796289</v>
       </c>
       <c r="D7" t="s">
         <v>307</v>
@@ -4467,7 +4483,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0.9183300479999992</v>
+        <v>0.9183300479999993</v>
       </c>
       <c r="C10">
         <v>0.5276111379852266</v>
@@ -4759,7 +4775,7 @@
         <v>0.5493573853596152</v>
       </c>
       <c r="C27">
-        <v>0.12397393947407208</v>
+        <v>0.12397393947407209</v>
       </c>
       <c r="D27" t="s">
         <v>307</v>
@@ -4807,7 +4823,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0.11937252307111525</v>
+        <v>0.11937252307111523</v>
       </c>
       <c r="C30">
         <v>0.5309979162455813</v>
@@ -4895,7 +4911,7 @@
         <v>0.2524134262230314</v>
       </c>
       <c r="C35">
-        <v>0.90150571565407</v>
+        <v>0.9015057156540699</v>
       </c>
       <c r="D35" t="s">
         <v>307</v>
@@ -4977,7 +4993,7 @@
         <v>49</v>
       </c>
       <c r="B40">
-        <v>0.20507174796366137</v>
+        <v>0.20507174796366134</v>
       </c>
       <c r="C40">
         <v>0.6341691748428233</v>
@@ -5031,7 +5047,7 @@
         <v>0.13572885912587274</v>
       </c>
       <c r="C43">
-        <v>0.9256900004446188</v>
+        <v>0.9256900004446187</v>
       </c>
       <c r="D43" t="s">
         <v>307</v>
@@ -5048,7 +5064,7 @@
         <v>0.5953842805560255</v>
       </c>
       <c r="C44">
-        <v>0.2102279526854728</v>
+        <v>0.21022795268547279</v>
       </c>
       <c r="D44" t="s">
         <v>307</v>
@@ -5096,7 +5112,7 @@
         <v>56</v>
       </c>
       <c r="B47">
-        <v>0.2347232479775536</v>
+        <v>0.23472324797755362</v>
       </c>
       <c r="C47">
         <v>0.42891321554258</v>
@@ -5266,7 +5282,7 @@
         <v>6</v>
       </c>
       <c r="B57">
-        <v>0.12151439149030609</v>
+        <v>0.12151439149030607</v>
       </c>
       <c r="C57">
         <v>0.7014218122942456</v>
@@ -5388,7 +5404,7 @@
         <v>0.13741827910602367</v>
       </c>
       <c r="C64">
-        <v>0.9695571264304772</v>
+        <v>0.9695571264304773</v>
       </c>
       <c r="D64" t="s">
         <v>307</v>
@@ -5522,6 +5538,3610 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E211"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D2">
+        <v>0.2864204577471846</v>
+      </c>
+      <c r="E2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D3">
+        <v>0.49630038105580987</v>
+      </c>
+      <c r="E3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4">
+        <v>0.8815889316377916</v>
+      </c>
+      <c r="E4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5">
+        <v>0.9034069008905734</v>
+      </c>
+      <c r="E5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6">
+        <v>0.6792889791769463</v>
+      </c>
+      <c r="E6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7">
+        <v>0.9034069008905926</v>
+      </c>
+      <c r="E7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8">
+        <v>0.9991750110336709</v>
+      </c>
+      <c r="E8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9">
+        <v>0.23638511885740576</v>
+      </c>
+      <c r="E9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10">
+        <v>0.247991169200535</v>
+      </c>
+      <c r="E10" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11">
+        <v>0.998095875005423</v>
+      </c>
+      <c r="E11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12">
+        <v>0.8844375386914635</v>
+      </c>
+      <c r="E12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>314</v>
+      </c>
+      <c r="C13" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13">
+        <v>0.8571741283136582</v>
+      </c>
+      <c r="E13" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D14">
+        <v>0.995543071984296</v>
+      </c>
+      <c r="E14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15">
+        <v>0.840291320354248</v>
+      </c>
+      <c r="E15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>314</v>
+      </c>
+      <c r="C16" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16">
+        <v>0.8829763971421055</v>
+      </c>
+      <c r="E16" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>312</v>
+      </c>
+      <c r="C17" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17">
+        <v>0.9948911036336393</v>
+      </c>
+      <c r="E17" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>313</v>
+      </c>
+      <c r="C18" t="s">
+        <v>307</v>
+      </c>
+      <c r="D18">
+        <v>0.9147956011765421</v>
+      </c>
+      <c r="E18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>314</v>
+      </c>
+      <c r="C19" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19">
+        <v>0.9493032392253428</v>
+      </c>
+      <c r="E19" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C20" t="s">
+        <v>307</v>
+      </c>
+      <c r="D20">
+        <v>0.9881925932803367</v>
+      </c>
+      <c r="E20" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21" t="s">
+        <v>307</v>
+      </c>
+      <c r="D21">
+        <v>0.9991541266965382</v>
+      </c>
+      <c r="E21" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" t="s">
+        <v>314</v>
+      </c>
+      <c r="C22" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22">
+        <v>0.9811464167635366</v>
+      </c>
+      <c r="E22" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" t="s">
+        <v>307</v>
+      </c>
+      <c r="D23">
+        <v>0.9953654645559817</v>
+      </c>
+      <c r="E23" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" t="s">
+        <v>307</v>
+      </c>
+      <c r="D24">
+        <v>0.9917808219607107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>314</v>
+      </c>
+      <c r="C25" t="s">
+        <v>307</v>
+      </c>
+      <c r="D25">
+        <v>0.999483713767341</v>
+      </c>
+      <c r="E25" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26" t="s">
+        <v>307</v>
+      </c>
+      <c r="D26">
+        <v>0.9812288012285462</v>
+      </c>
+      <c r="E26" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" t="s">
+        <v>313</v>
+      </c>
+      <c r="C27" t="s">
+        <v>307</v>
+      </c>
+      <c r="D27">
+        <v>0.643815027482008</v>
+      </c>
+      <c r="E27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" t="s">
+        <v>314</v>
+      </c>
+      <c r="C28" t="s">
+        <v>307</v>
+      </c>
+      <c r="D28">
+        <v>0.5406746684958741</v>
+      </c>
+      <c r="E28" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>312</v>
+      </c>
+      <c r="C29" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29">
+        <v>0.6702966080911591</v>
+      </c>
+      <c r="E29" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C30" t="s">
+        <v>307</v>
+      </c>
+      <c r="D30">
+        <v>0.9332349874375161</v>
+      </c>
+      <c r="E30" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>314</v>
+      </c>
+      <c r="C31" t="s">
+        <v>307</v>
+      </c>
+      <c r="D31">
+        <v>0.8619786885269487</v>
+      </c>
+      <c r="E31" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" t="s">
+        <v>307</v>
+      </c>
+      <c r="D32">
+        <v>0.9823815756669673</v>
+      </c>
+      <c r="E32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" t="s">
+        <v>307</v>
+      </c>
+      <c r="D33">
+        <v>0.8152887011877057</v>
+      </c>
+      <c r="E33" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>314</v>
+      </c>
+      <c r="C34" t="s">
+        <v>307</v>
+      </c>
+      <c r="D34">
+        <v>0.9006518922303046</v>
+      </c>
+      <c r="E34" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>312</v>
+      </c>
+      <c r="C35" t="s">
+        <v>307</v>
+      </c>
+      <c r="D35">
+        <v>0.968262655094916</v>
+      </c>
+      <c r="E35" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>313</v>
+      </c>
+      <c r="C36" t="s">
+        <v>307</v>
+      </c>
+      <c r="D36">
+        <v>0.8062836954689447</v>
+      </c>
+      <c r="E36" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>314</v>
+      </c>
+      <c r="C37" t="s">
+        <v>307</v>
+      </c>
+      <c r="D37">
+        <v>0.9190602570241868</v>
+      </c>
+      <c r="E37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" t="s">
+        <v>312</v>
+      </c>
+      <c r="C38" t="s">
+        <v>309</v>
+      </c>
+      <c r="D38">
+        <v>0.761322176766294</v>
+      </c>
+      <c r="E38" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" t="s">
+        <v>313</v>
+      </c>
+      <c r="C39" t="s">
+        <v>309</v>
+      </c>
+      <c r="D39">
+        <v>0.4158399480531523</v>
+      </c>
+      <c r="E39" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" t="s">
+        <v>314</v>
+      </c>
+      <c r="C40" t="s">
+        <v>309</v>
+      </c>
+      <c r="D40">
+        <v>0.23066539928924412</v>
+      </c>
+      <c r="E40" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" t="s">
+        <v>312</v>
+      </c>
+      <c r="C41" t="s">
+        <v>307</v>
+      </c>
+      <c r="D41">
+        <v>0.9836779998244929</v>
+      </c>
+      <c r="E41" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>313</v>
+      </c>
+      <c r="C42" t="s">
+        <v>307</v>
+      </c>
+      <c r="D42">
+        <v>0.8074789338794317</v>
+      </c>
+      <c r="E42" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" t="s">
+        <v>314</v>
+      </c>
+      <c r="C43" t="s">
+        <v>307</v>
+      </c>
+      <c r="D43">
+        <v>0.8913180773474063</v>
+      </c>
+      <c r="E43" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>312</v>
+      </c>
+      <c r="C44" t="s">
+        <v>307</v>
+      </c>
+      <c r="D44">
+        <v>0.9900732656378581</v>
+      </c>
+      <c r="E44" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>313</v>
+      </c>
+      <c r="C45" t="s">
+        <v>307</v>
+      </c>
+      <c r="D45">
+        <v>0.8356812914161837</v>
+      </c>
+      <c r="E45" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C46" t="s">
+        <v>307</v>
+      </c>
+      <c r="D46">
+        <v>0.8984171286458912</v>
+      </c>
+      <c r="E46" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B47" t="s">
+        <v>312</v>
+      </c>
+      <c r="C47" t="s">
+        <v>307</v>
+      </c>
+      <c r="D47">
+        <v>0.8021467977825301</v>
+      </c>
+      <c r="E47" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" t="s">
+        <v>313</v>
+      </c>
+      <c r="C48" t="s">
+        <v>307</v>
+      </c>
+      <c r="D48">
+        <v>0.856544406395305</v>
+      </c>
+      <c r="E48" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" t="s">
+        <v>307</v>
+      </c>
+      <c r="D49">
+        <v>0.5049451426568597</v>
+      </c>
+      <c r="E49" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" t="s">
+        <v>312</v>
+      </c>
+      <c r="C50" t="s">
+        <v>307</v>
+      </c>
+      <c r="D50">
+        <v>0.8740030456273548</v>
+      </c>
+      <c r="E50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" t="s">
+        <v>313</v>
+      </c>
+      <c r="C51" t="s">
+        <v>307</v>
+      </c>
+      <c r="D51">
+        <v>0.8740030456273548</v>
+      </c>
+      <c r="E51" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>314</v>
+      </c>
+      <c r="C52" t="s">
+        <v>307</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" t="s">
+        <v>312</v>
+      </c>
+      <c r="C53" t="s">
+        <v>307</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s">
+        <v>313</v>
+      </c>
+      <c r="C54" t="s">
+        <v>307</v>
+      </c>
+      <c r="D54">
+        <v>0.7684324622573119</v>
+      </c>
+      <c r="E54" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>314</v>
+      </c>
+      <c r="C55" t="s">
+        <v>307</v>
+      </c>
+      <c r="D55">
+        <v>0.7684324622573119</v>
+      </c>
+      <c r="E55" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" t="s">
+        <v>312</v>
+      </c>
+      <c r="C56" t="s">
+        <v>307</v>
+      </c>
+      <c r="D56">
+        <v>0.25406649637572465</v>
+      </c>
+      <c r="E56" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" t="s">
+        <v>313</v>
+      </c>
+      <c r="C57" t="s">
+        <v>307</v>
+      </c>
+      <c r="D57">
+        <v>0.5161565893562248</v>
+      </c>
+      <c r="E57" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" t="s">
+        <v>314</v>
+      </c>
+      <c r="C58" t="s">
+        <v>307</v>
+      </c>
+      <c r="D58">
+        <v>0.8152761511275898</v>
+      </c>
+      <c r="E58" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>30</v>
+      </c>
+      <c r="B59" t="s">
+        <v>312</v>
+      </c>
+      <c r="C59" t="s">
+        <v>307</v>
+      </c>
+      <c r="D59">
+        <v>0.2651269440446462</v>
+      </c>
+      <c r="E59" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>313</v>
+      </c>
+      <c r="C60" t="s">
+        <v>307</v>
+      </c>
+      <c r="D60">
+        <v>0.9999781327078274</v>
+      </c>
+      <c r="E60" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>30</v>
+      </c>
+      <c r="B61" t="s">
+        <v>314</v>
+      </c>
+      <c r="C61" t="s">
+        <v>307</v>
+      </c>
+      <c r="D61">
+        <v>0.2630796467230846</v>
+      </c>
+      <c r="E61" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" t="s">
+        <v>312</v>
+      </c>
+      <c r="C62" t="s">
+        <v>307</v>
+      </c>
+      <c r="D62">
+        <v>0.29498693211328375</v>
+      </c>
+      <c r="E62" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" t="s">
+        <v>313</v>
+      </c>
+      <c r="C63" t="s">
+        <v>307</v>
+      </c>
+      <c r="D63">
+        <v>0.9891130478387883</v>
+      </c>
+      <c r="E63" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>31</v>
+      </c>
+      <c r="B64" t="s">
+        <v>314</v>
+      </c>
+      <c r="C64" t="s">
+        <v>307</v>
+      </c>
+      <c r="D64">
+        <v>0.24829685499880216</v>
+      </c>
+      <c r="E64" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" t="s">
+        <v>312</v>
+      </c>
+      <c r="C65" t="s">
+        <v>307</v>
+      </c>
+      <c r="D65">
+        <v>0.7699954844620485</v>
+      </c>
+      <c r="E65" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>32</v>
+      </c>
+      <c r="B66" t="s">
+        <v>313</v>
+      </c>
+      <c r="C66" t="s">
+        <v>307</v>
+      </c>
+      <c r="D66">
+        <v>0.9642817376171685</v>
+      </c>
+      <c r="E66" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" t="s">
+        <v>314</v>
+      </c>
+      <c r="C67" t="s">
+        <v>307</v>
+      </c>
+      <c r="D67">
+        <v>0.8976836460875339</v>
+      </c>
+      <c r="E67" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" t="s">
+        <v>312</v>
+      </c>
+      <c r="C68" t="s">
+        <v>307</v>
+      </c>
+      <c r="D68">
+        <v>0.9872018923845114</v>
+      </c>
+      <c r="E68" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" t="s">
+        <v>313</v>
+      </c>
+      <c r="C69" t="s">
+        <v>307</v>
+      </c>
+      <c r="D69">
+        <v>0.6714283245602213</v>
+      </c>
+      <c r="E69" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" t="s">
+        <v>314</v>
+      </c>
+      <c r="C70" t="s">
+        <v>307</v>
+      </c>
+      <c r="D70">
+        <v>0.5851545575175037</v>
+      </c>
+      <c r="E70" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" t="s">
+        <v>312</v>
+      </c>
+      <c r="C71" t="s">
+        <v>307</v>
+      </c>
+      <c r="D71">
+        <v>0.2314767524726845</v>
+      </c>
+      <c r="E71" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>34</v>
+      </c>
+      <c r="B72" t="s">
+        <v>313</v>
+      </c>
+      <c r="C72" t="s">
+        <v>307</v>
+      </c>
+      <c r="D72">
+        <v>0.6661790260735732</v>
+      </c>
+      <c r="E72" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>34</v>
+      </c>
+      <c r="B73" t="s">
+        <v>314</v>
+      </c>
+      <c r="C73" t="s">
+        <v>307</v>
+      </c>
+      <c r="D73">
+        <v>0.6227400526263016</v>
+      </c>
+      <c r="E73" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B74" t="s">
+        <v>312</v>
+      </c>
+      <c r="C74" t="s">
+        <v>307</v>
+      </c>
+      <c r="D74">
+        <v>0.2974341479260717</v>
+      </c>
+      <c r="E74" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>35</v>
+      </c>
+      <c r="B75" t="s">
+        <v>313</v>
+      </c>
+      <c r="C75" t="s">
+        <v>307</v>
+      </c>
+      <c r="D75">
+        <v>0.7024676856033036</v>
+      </c>
+      <c r="E75" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" t="s">
+        <v>314</v>
+      </c>
+      <c r="C76" t="s">
+        <v>307</v>
+      </c>
+      <c r="D76">
+        <v>0.7024676856033021</v>
+      </c>
+      <c r="E76" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" t="s">
+        <v>312</v>
+      </c>
+      <c r="C77" t="s">
+        <v>307</v>
+      </c>
+      <c r="D77">
+        <v>0.10813159266081063</v>
+      </c>
+      <c r="E77" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" t="s">
+        <v>313</v>
+      </c>
+      <c r="C78" t="s">
+        <v>307</v>
+      </c>
+      <c r="D78">
+        <v>0.5187892008283557</v>
+      </c>
+      <c r="E78" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>36</v>
+      </c>
+      <c r="B79" t="s">
+        <v>314</v>
+      </c>
+      <c r="C79" t="s">
+        <v>307</v>
+      </c>
+      <c r="D79">
+        <v>0.44554218332607276</v>
+      </c>
+      <c r="E79" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" t="s">
+        <v>312</v>
+      </c>
+      <c r="C80" t="s">
+        <v>307</v>
+      </c>
+      <c r="D80">
+        <v>0.7859466779619335</v>
+      </c>
+      <c r="E80" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>37</v>
+      </c>
+      <c r="B81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C81" t="s">
+        <v>307</v>
+      </c>
+      <c r="D81">
+        <v>0.8740509553360496</v>
+      </c>
+      <c r="E81" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>37</v>
+      </c>
+      <c r="B82" t="s">
+        <v>314</v>
+      </c>
+      <c r="C82" t="s">
+        <v>307</v>
+      </c>
+      <c r="D82">
+        <v>0.9833120511222283</v>
+      </c>
+      <c r="E82" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" t="s">
+        <v>312</v>
+      </c>
+      <c r="C83" t="s">
+        <v>307</v>
+      </c>
+      <c r="D83">
+        <v>0.9855197109644568</v>
+      </c>
+      <c r="E83" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" t="s">
+        <v>313</v>
+      </c>
+      <c r="C84" t="s">
+        <v>307</v>
+      </c>
+      <c r="D84">
+        <v>0.7691934810768332</v>
+      </c>
+      <c r="E84" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>38</v>
+      </c>
+      <c r="B85" t="s">
+        <v>314</v>
+      </c>
+      <c r="C85" t="s">
+        <v>307</v>
+      </c>
+      <c r="D85">
+        <v>0.6778407507274775</v>
+      </c>
+      <c r="E85" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" t="s">
+        <v>312</v>
+      </c>
+      <c r="C86" t="s">
+        <v>307</v>
+      </c>
+      <c r="D86">
+        <v>0.9656554679082063</v>
+      </c>
+      <c r="E86" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>39</v>
+      </c>
+      <c r="B87" t="s">
+        <v>313</v>
+      </c>
+      <c r="C87" t="s">
+        <v>307</v>
+      </c>
+      <c r="D87">
+        <v>0.672277987935961</v>
+      </c>
+      <c r="E87" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>39</v>
+      </c>
+      <c r="B88" t="s">
+        <v>314</v>
+      </c>
+      <c r="C88" t="s">
+        <v>307</v>
+      </c>
+      <c r="D88">
+        <v>0.5317068202770144</v>
+      </c>
+      <c r="E88" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>312</v>
+      </c>
+      <c r="C89" t="s">
+        <v>307</v>
+      </c>
+      <c r="D89">
+        <v>0.9473383736992443</v>
+      </c>
+      <c r="E89" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" t="s">
+        <v>313</v>
+      </c>
+      <c r="C90" t="s">
+        <v>307</v>
+      </c>
+      <c r="D90">
+        <v>0.6623572375653968</v>
+      </c>
+      <c r="E90" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" t="s">
+        <v>314</v>
+      </c>
+      <c r="C91" t="s">
+        <v>307</v>
+      </c>
+      <c r="D91">
+        <v>0.4899881080532088</v>
+      </c>
+      <c r="E91" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>41</v>
+      </c>
+      <c r="B92" t="s">
+        <v>312</v>
+      </c>
+      <c r="C92" t="s">
+        <v>309</v>
+      </c>
+      <c r="D92">
+        <v>0.9338799293846354</v>
+      </c>
+      <c r="E92" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>41</v>
+      </c>
+      <c r="B93" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" t="s">
+        <v>309</v>
+      </c>
+      <c r="D93">
+        <v>0.5784169227398279</v>
+      </c>
+      <c r="E93" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>41</v>
+      </c>
+      <c r="B94" t="s">
+        <v>314</v>
+      </c>
+      <c r="C94" t="s">
+        <v>309</v>
+      </c>
+      <c r="D94">
+        <v>0.512984088844326</v>
+      </c>
+      <c r="E94" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>42</v>
+      </c>
+      <c r="B95" t="s">
+        <v>312</v>
+      </c>
+      <c r="C95" t="s">
+        <v>309</v>
+      </c>
+      <c r="D95">
+        <v>0.9338799293846385</v>
+      </c>
+      <c r="E95" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" t="s">
+        <v>313</v>
+      </c>
+      <c r="C96" t="s">
+        <v>309</v>
+      </c>
+      <c r="D96">
+        <v>0.5784169227398224</v>
+      </c>
+      <c r="E96" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>42</v>
+      </c>
+      <c r="B97" t="s">
+        <v>314</v>
+      </c>
+      <c r="C97" t="s">
+        <v>309</v>
+      </c>
+      <c r="D97">
+        <v>0.5129840888443223</v>
+      </c>
+      <c r="E97" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>43</v>
+      </c>
+      <c r="B98" t="s">
+        <v>312</v>
+      </c>
+      <c r="C98" t="s">
+        <v>307</v>
+      </c>
+      <c r="D98">
+        <v>0.9959798388234644</v>
+      </c>
+      <c r="E98" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>43</v>
+      </c>
+      <c r="B99" t="s">
+        <v>313</v>
+      </c>
+      <c r="C99" t="s">
+        <v>307</v>
+      </c>
+      <c r="D99">
+        <v>0.7716870204941252</v>
+      </c>
+      <c r="E99" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>43</v>
+      </c>
+      <c r="B100" t="s">
+        <v>314</v>
+      </c>
+      <c r="C100" t="s">
+        <v>307</v>
+      </c>
+      <c r="D100">
+        <v>0.724218608328353</v>
+      </c>
+      <c r="E100" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>44</v>
+      </c>
+      <c r="B101" t="s">
+        <v>312</v>
+      </c>
+      <c r="C101" t="s">
+        <v>307</v>
+      </c>
+      <c r="D101">
+        <v>0.9951980268878277</v>
+      </c>
+      <c r="E101" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>44</v>
+      </c>
+      <c r="B102" t="s">
+        <v>313</v>
+      </c>
+      <c r="C102" t="s">
+        <v>307</v>
+      </c>
+      <c r="D102">
+        <v>0.9379505090749236</v>
+      </c>
+      <c r="E102" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>44</v>
+      </c>
+      <c r="B103" t="s">
+        <v>314</v>
+      </c>
+      <c r="C103" t="s">
+        <v>307</v>
+      </c>
+      <c r="D103">
+        <v>0.9020656095781052</v>
+      </c>
+      <c r="E103" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>45</v>
+      </c>
+      <c r="B104" t="s">
+        <v>312</v>
+      </c>
+      <c r="C104" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104">
+        <v>0.7792550776669778</v>
+      </c>
+      <c r="E104" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>45</v>
+      </c>
+      <c r="B105" t="s">
+        <v>313</v>
+      </c>
+      <c r="C105" t="s">
+        <v>307</v>
+      </c>
+      <c r="D105">
+        <v>0.9716205113604405</v>
+      </c>
+      <c r="E105" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>45</v>
+      </c>
+      <c r="B106" t="s">
+        <v>314</v>
+      </c>
+      <c r="C106" t="s">
+        <v>307</v>
+      </c>
+      <c r="D106">
+        <v>0.8927120316737114</v>
+      </c>
+      <c r="E106" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107" t="s">
+        <v>307</v>
+      </c>
+      <c r="D107">
+        <v>0.6157453480554935</v>
+      </c>
+      <c r="E107" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" t="s">
+        <v>313</v>
+      </c>
+      <c r="C108" t="s">
+        <v>307</v>
+      </c>
+      <c r="D108">
+        <v>0.8671209263999232</v>
+      </c>
+      <c r="E108" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>46</v>
+      </c>
+      <c r="B109" t="s">
+        <v>314</v>
+      </c>
+      <c r="C109" t="s">
+        <v>307</v>
+      </c>
+      <c r="D109">
+        <v>0.8904589809662258</v>
+      </c>
+      <c r="E109" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>47</v>
+      </c>
+      <c r="B110" t="s">
+        <v>312</v>
+      </c>
+      <c r="C110" t="s">
+        <v>307</v>
+      </c>
+      <c r="D110">
+        <v>0.16714505567197968</v>
+      </c>
+      <c r="E110" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>47</v>
+      </c>
+      <c r="B111" t="s">
+        <v>313</v>
+      </c>
+      <c r="C111" t="s">
+        <v>307</v>
+      </c>
+      <c r="D111">
+        <v>0.39065696180398624</v>
+      </c>
+      <c r="E111" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>47</v>
+      </c>
+      <c r="B112" t="s">
+        <v>314</v>
+      </c>
+      <c r="C112" t="s">
+        <v>307</v>
+      </c>
+      <c r="D112">
+        <v>0.7747518910216171</v>
+      </c>
+      <c r="E112" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>48</v>
+      </c>
+      <c r="B113" t="s">
+        <v>312</v>
+      </c>
+      <c r="C113" t="s">
+        <v>307</v>
+      </c>
+      <c r="D113">
+        <v>0.4380266494481072</v>
+      </c>
+      <c r="E113" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>48</v>
+      </c>
+      <c r="B114" t="s">
+        <v>313</v>
+      </c>
+      <c r="C114" t="s">
+        <v>307</v>
+      </c>
+      <c r="D114">
+        <v>0.997840582956019</v>
+      </c>
+      <c r="E114" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" t="s">
+        <v>314</v>
+      </c>
+      <c r="C115" t="s">
+        <v>307</v>
+      </c>
+      <c r="D115">
+        <v>0.4086766929879584</v>
+      </c>
+      <c r="E115" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>49</v>
+      </c>
+      <c r="B116" t="s">
+        <v>312</v>
+      </c>
+      <c r="C116" t="s">
+        <v>307</v>
+      </c>
+      <c r="D116">
+        <v>0.9998200174664774</v>
+      </c>
+      <c r="E116" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>49</v>
+      </c>
+      <c r="B117" t="s">
+        <v>313</v>
+      </c>
+      <c r="C117" t="s">
+        <v>307</v>
+      </c>
+      <c r="D117">
+        <v>0.6782711987568065</v>
+      </c>
+      <c r="E117" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>49</v>
+      </c>
+      <c r="B118" t="s">
+        <v>314</v>
+      </c>
+      <c r="C118" t="s">
+        <v>307</v>
+      </c>
+      <c r="D118">
+        <v>0.688541866545658</v>
+      </c>
+      <c r="E118" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>50</v>
+      </c>
+      <c r="B119" t="s">
+        <v>312</v>
+      </c>
+      <c r="C119" t="s">
+        <v>307</v>
+      </c>
+      <c r="D119">
+        <v>0.3856413213246297</v>
+      </c>
+      <c r="E119" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>50</v>
+      </c>
+      <c r="B120" t="s">
+        <v>313</v>
+      </c>
+      <c r="C120" t="s">
+        <v>307</v>
+      </c>
+      <c r="D120">
+        <v>0.9826102565737673</v>
+      </c>
+      <c r="E120" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>50</v>
+      </c>
+      <c r="B121" t="s">
+        <v>314</v>
+      </c>
+      <c r="C121" t="s">
+        <v>307</v>
+      </c>
+      <c r="D121">
+        <v>0.46971716848025435</v>
+      </c>
+      <c r="E121" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>51</v>
+      </c>
+      <c r="B122" t="s">
+        <v>312</v>
+      </c>
+      <c r="C122" t="s">
+        <v>307</v>
+      </c>
+      <c r="D122">
+        <v>0.9167309630636207</v>
+      </c>
+      <c r="E122" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>51</v>
+      </c>
+      <c r="B123" t="s">
+        <v>313</v>
+      </c>
+      <c r="C123" t="s">
+        <v>307</v>
+      </c>
+      <c r="D123">
+        <v>0.6332003805587347</v>
+      </c>
+      <c r="E123" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>51</v>
+      </c>
+      <c r="B124" t="s">
+        <v>314</v>
+      </c>
+      <c r="C124" t="s">
+        <v>307</v>
+      </c>
+      <c r="D124">
+        <v>0.4228071063192782</v>
+      </c>
+      <c r="E124" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>52</v>
+      </c>
+      <c r="B125" t="s">
+        <v>312</v>
+      </c>
+      <c r="C125" t="s">
+        <v>307</v>
+      </c>
+      <c r="D125">
+        <v>0.9206761871773462</v>
+      </c>
+      <c r="E125" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>52</v>
+      </c>
+      <c r="B126" t="s">
+        <v>313</v>
+      </c>
+      <c r="C126" t="s">
+        <v>307</v>
+      </c>
+      <c r="D126">
+        <v>0.9896301755185628</v>
+      </c>
+      <c r="E126" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>52</v>
+      </c>
+      <c r="B127" t="s">
+        <v>314</v>
+      </c>
+      <c r="C127" t="s">
+        <v>307</v>
+      </c>
+      <c r="D127">
+        <v>0.9657127678247207</v>
+      </c>
+      <c r="E127" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>53</v>
+      </c>
+      <c r="B128" t="s">
+        <v>312</v>
+      </c>
+      <c r="C128" t="s">
+        <v>307</v>
+      </c>
+      <c r="D128">
+        <v>0.7452942643288996</v>
+      </c>
+      <c r="E128" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>53</v>
+      </c>
+      <c r="B129" t="s">
+        <v>313</v>
+      </c>
+      <c r="C129" t="s">
+        <v>307</v>
+      </c>
+      <c r="D129">
+        <v>0.19257723946557337</v>
+      </c>
+      <c r="E129" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>53</v>
+      </c>
+      <c r="B130" t="s">
+        <v>314</v>
+      </c>
+      <c r="C130" t="s">
+        <v>307</v>
+      </c>
+      <c r="D130">
+        <v>0.46871323522361574</v>
+      </c>
+      <c r="E130" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>54</v>
+      </c>
+      <c r="B131" t="s">
+        <v>312</v>
+      </c>
+      <c r="C131" t="s">
+        <v>309</v>
+      </c>
+      <c r="D131">
+        <v>0.39696237929324474</v>
+      </c>
+      <c r="E131" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>54</v>
+      </c>
+      <c r="B132" t="s">
+        <v>313</v>
+      </c>
+      <c r="C132" t="s">
+        <v>309</v>
+      </c>
+      <c r="D132">
+        <v>0.5900518148318962</v>
+      </c>
+      <c r="E132" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>54</v>
+      </c>
+      <c r="B133" t="s">
+        <v>314</v>
+      </c>
+      <c r="C133" t="s">
+        <v>309</v>
+      </c>
+      <c r="D133">
+        <v>0.77230854832815</v>
+      </c>
+      <c r="E133" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>55</v>
+      </c>
+      <c r="B134" t="s">
+        <v>312</v>
+      </c>
+      <c r="C134" t="s">
+        <v>307</v>
+      </c>
+      <c r="D134">
+        <v>0.8868742739734841</v>
+      </c>
+      <c r="E134" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>55</v>
+      </c>
+      <c r="B135" t="s">
+        <v>313</v>
+      </c>
+      <c r="C135" t="s">
+        <v>307</v>
+      </c>
+      <c r="D135">
+        <v>0.29261454598337644</v>
+      </c>
+      <c r="E135" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>55</v>
+      </c>
+      <c r="B136" t="s">
+        <v>314</v>
+      </c>
+      <c r="C136" t="s">
+        <v>307</v>
+      </c>
+      <c r="D136">
+        <v>0.4993181540006596</v>
+      </c>
+      <c r="E136" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>56</v>
+      </c>
+      <c r="B137" t="s">
+        <v>312</v>
+      </c>
+      <c r="C137" t="s">
+        <v>307</v>
+      </c>
+      <c r="D137">
+        <v>0.41258716764396364</v>
+      </c>
+      <c r="E137" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>56</v>
+      </c>
+      <c r="B138" t="s">
+        <v>313</v>
+      </c>
+      <c r="C138" t="s">
+        <v>307</v>
+      </c>
+      <c r="D138">
+        <v>0.9012458257816589</v>
+      </c>
+      <c r="E138" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>56</v>
+      </c>
+      <c r="B139" t="s">
+        <v>314</v>
+      </c>
+      <c r="C139" t="s">
+        <v>307</v>
+      </c>
+      <c r="D139">
+        <v>0.6423118165295291</v>
+      </c>
+      <c r="E139" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>57</v>
+      </c>
+      <c r="B140" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" t="s">
+        <v>307</v>
+      </c>
+      <c r="D140">
+        <v>0.13776511157102378</v>
+      </c>
+      <c r="E140" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>57</v>
+      </c>
+      <c r="B141" t="s">
+        <v>313</v>
+      </c>
+      <c r="C141" t="s">
+        <v>307</v>
+      </c>
+      <c r="D141">
+        <v>0.6843864764155808</v>
+      </c>
+      <c r="E141" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>57</v>
+      </c>
+      <c r="B142" t="s">
+        <v>314</v>
+      </c>
+      <c r="C142" t="s">
+        <v>307</v>
+      </c>
+      <c r="D142">
+        <v>0.39501878301279547</v>
+      </c>
+      <c r="E142" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>58</v>
+      </c>
+      <c r="B143" t="s">
+        <v>312</v>
+      </c>
+      <c r="C143" t="s">
+        <v>309</v>
+      </c>
+      <c r="D143">
+        <v>0.9741557354263479</v>
+      </c>
+      <c r="E143" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>58</v>
+      </c>
+      <c r="B144" t="s">
+        <v>313</v>
+      </c>
+      <c r="C144" t="s">
+        <v>309</v>
+      </c>
+      <c r="D144">
+        <v>0.9992312521286567</v>
+      </c>
+      <c r="E144" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>58</v>
+      </c>
+      <c r="B145" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145" t="s">
+        <v>309</v>
+      </c>
+      <c r="D145">
+        <v>0.7006474784461909</v>
+      </c>
+      <c r="E145" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>59</v>
+      </c>
+      <c r="B146" t="s">
+        <v>312</v>
+      </c>
+      <c r="C146" t="s">
+        <v>307</v>
+      </c>
+      <c r="D146">
+        <v>0.9719612661748843</v>
+      </c>
+      <c r="E146" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>59</v>
+      </c>
+      <c r="B147" t="s">
+        <v>313</v>
+      </c>
+      <c r="C147" t="s">
+        <v>307</v>
+      </c>
+      <c r="D147">
+        <v>0.22479929476270133</v>
+      </c>
+      <c r="E147" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>59</v>
+      </c>
+      <c r="B148" t="s">
+        <v>314</v>
+      </c>
+      <c r="C148" t="s">
+        <v>307</v>
+      </c>
+      <c r="D148">
+        <v>0.29733511371222954</v>
+      </c>
+      <c r="E148" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>60</v>
+      </c>
+      <c r="B149" t="s">
+        <v>312</v>
+      </c>
+      <c r="C149" t="s">
+        <v>307</v>
+      </c>
+      <c r="D149">
+        <v>0.5643829314956511</v>
+      </c>
+      <c r="E149" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>60</v>
+      </c>
+      <c r="B150" t="s">
+        <v>313</v>
+      </c>
+      <c r="C150" t="s">
+        <v>307</v>
+      </c>
+      <c r="D150">
+        <v>0.9408612993293761</v>
+      </c>
+      <c r="E150" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>60</v>
+      </c>
+      <c r="B151" t="s">
+        <v>314</v>
+      </c>
+      <c r="C151" t="s">
+        <v>307</v>
+      </c>
+      <c r="D151">
+        <v>0.39645763590757044</v>
+      </c>
+      <c r="E151" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>61</v>
+      </c>
+      <c r="B152" t="s">
+        <v>312</v>
+      </c>
+      <c r="C152" t="s">
+        <v>307</v>
+      </c>
+      <c r="D152">
+        <v>0.39173396922219605</v>
+      </c>
+      <c r="E152" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>61</v>
+      </c>
+      <c r="B153" t="s">
+        <v>313</v>
+      </c>
+      <c r="C153" t="s">
+        <v>307</v>
+      </c>
+      <c r="D153">
+        <v>0.171054019291091</v>
+      </c>
+      <c r="E153" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>61</v>
+      </c>
+      <c r="B154" t="s">
+        <v>314</v>
+      </c>
+      <c r="C154" t="s">
+        <v>307</v>
+      </c>
+      <c r="D154">
+        <v>0.7833046474424488</v>
+      </c>
+      <c r="E154" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>62</v>
+      </c>
+      <c r="B155" t="s">
+        <v>312</v>
+      </c>
+      <c r="C155" t="s">
+        <v>307</v>
+      </c>
+      <c r="D155">
+        <v>0.9916878875361849</v>
+      </c>
+      <c r="E155" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>62</v>
+      </c>
+      <c r="B156" t="s">
+        <v>313</v>
+      </c>
+      <c r="C156" t="s">
+        <v>307</v>
+      </c>
+      <c r="D156">
+        <v>0.7165081618649936</v>
+      </c>
+      <c r="E156" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>62</v>
+      </c>
+      <c r="B157" t="s">
+        <v>314</v>
+      </c>
+      <c r="C157" t="s">
+        <v>307</v>
+      </c>
+      <c r="D157">
+        <v>0.7846762375591474</v>
+      </c>
+      <c r="E157" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>63</v>
+      </c>
+      <c r="B158" t="s">
+        <v>312</v>
+      </c>
+      <c r="C158" t="s">
+        <v>307</v>
+      </c>
+      <c r="D158">
+        <v>0.9782872875243429</v>
+      </c>
+      <c r="E158" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>63</v>
+      </c>
+      <c r="B159" t="s">
+        <v>313</v>
+      </c>
+      <c r="C159" t="s">
+        <v>307</v>
+      </c>
+      <c r="D159">
+        <v>0.8125222582285168</v>
+      </c>
+      <c r="E159" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>63</v>
+      </c>
+      <c r="B160" t="s">
+        <v>314</v>
+      </c>
+      <c r="C160" t="s">
+        <v>307</v>
+      </c>
+      <c r="D160">
+        <v>0.7027660527974398</v>
+      </c>
+      <c r="E160" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>64</v>
+      </c>
+      <c r="B161" t="s">
+        <v>312</v>
+      </c>
+      <c r="C161" t="s">
+        <v>307</v>
+      </c>
+      <c r="D161">
+        <v>0.8628454002784922</v>
+      </c>
+      <c r="E161" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>64</v>
+      </c>
+      <c r="B162" t="s">
+        <v>313</v>
+      </c>
+      <c r="C162" t="s">
+        <v>307</v>
+      </c>
+      <c r="D162">
+        <v>0.9019187570630613</v>
+      </c>
+      <c r="E162" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>64</v>
+      </c>
+      <c r="B163" t="s">
+        <v>314</v>
+      </c>
+      <c r="C163" t="s">
+        <v>307</v>
+      </c>
+      <c r="D163">
+        <v>0.995808486869371</v>
+      </c>
+      <c r="E163" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>65</v>
+      </c>
+      <c r="B164" t="s">
+        <v>312</v>
+      </c>
+      <c r="C164" t="s">
+        <v>307</v>
+      </c>
+      <c r="D164">
+        <v>0.5572219435788416</v>
+      </c>
+      <c r="E164" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>65</v>
+      </c>
+      <c r="B165" t="s">
+        <v>313</v>
+      </c>
+      <c r="C165" t="s">
+        <v>307</v>
+      </c>
+      <c r="D165">
+        <v>0.9519282937725422</v>
+      </c>
+      <c r="E165" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>65</v>
+      </c>
+      <c r="B166" t="s">
+        <v>314</v>
+      </c>
+      <c r="C166" t="s">
+        <v>307</v>
+      </c>
+      <c r="D166">
+        <v>0.7260293886652495</v>
+      </c>
+      <c r="E166" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>6</v>
+      </c>
+      <c r="B167" t="s">
+        <v>312</v>
+      </c>
+      <c r="C167" t="s">
+        <v>307</v>
+      </c>
+      <c r="D167">
+        <v>0.6826512227728152</v>
+      </c>
+      <c r="E167" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>6</v>
+      </c>
+      <c r="B168" t="s">
+        <v>313</v>
+      </c>
+      <c r="C168" t="s">
+        <v>307</v>
+      </c>
+      <c r="D168">
+        <v>0.9420295479277405</v>
+      </c>
+      <c r="E168" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>6</v>
+      </c>
+      <c r="B169" t="s">
+        <v>314</v>
+      </c>
+      <c r="C169" t="s">
+        <v>307</v>
+      </c>
+      <c r="D169">
+        <v>0.8602747468732796</v>
+      </c>
+      <c r="E169" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" t="s">
+        <v>312</v>
+      </c>
+      <c r="C170" t="s">
+        <v>307</v>
+      </c>
+      <c r="D170">
+        <v>0.2576314100065805</v>
+      </c>
+      <c r="E170" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" t="s">
+        <v>313</v>
+      </c>
+      <c r="C171" t="s">
+        <v>307</v>
+      </c>
+      <c r="D171">
+        <v>0.5125283727530696</v>
+      </c>
+      <c r="E171" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" t="s">
+        <v>314</v>
+      </c>
+      <c r="C172" t="s">
+        <v>307</v>
+      </c>
+      <c r="D172">
+        <v>0.8246678144170507</v>
+      </c>
+      <c r="E172" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>66</v>
+      </c>
+      <c r="B173" t="s">
+        <v>312</v>
+      </c>
+      <c r="C173" t="s">
+        <v>307</v>
+      </c>
+      <c r="D173">
+        <v>0.7863632392655668</v>
+      </c>
+      <c r="E173" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>66</v>
+      </c>
+      <c r="B174" t="s">
+        <v>313</v>
+      </c>
+      <c r="C174" t="s">
+        <v>307</v>
+      </c>
+      <c r="D174">
+        <v>0.8571570082242688</v>
+      </c>
+      <c r="E174" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>66</v>
+      </c>
+      <c r="B175" t="s">
+        <v>314</v>
+      </c>
+      <c r="C175" t="s">
+        <v>307</v>
+      </c>
+      <c r="D175">
+        <v>0.4903098626401964</v>
+      </c>
+      <c r="E175" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>67</v>
+      </c>
+      <c r="B176" t="s">
+        <v>312</v>
+      </c>
+      <c r="C176" t="s">
+        <v>307</v>
+      </c>
+      <c r="D176">
+        <v>0.7653397035417706</v>
+      </c>
+      <c r="E176" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>67</v>
+      </c>
+      <c r="B177" t="s">
+        <v>313</v>
+      </c>
+      <c r="C177" t="s">
+        <v>307</v>
+      </c>
+      <c r="D177">
+        <v>0.952920552953525</v>
+      </c>
+      <c r="E177" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>67</v>
+      </c>
+      <c r="B178" t="s">
+        <v>314</v>
+      </c>
+      <c r="C178" t="s">
+        <v>307</v>
+      </c>
+      <c r="D178">
+        <v>0.9104835174043856</v>
+      </c>
+      <c r="E178" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>68</v>
+      </c>
+      <c r="B179" t="s">
+        <v>312</v>
+      </c>
+      <c r="C179" t="s">
+        <v>307</v>
+      </c>
+      <c r="D179">
+        <v>0.4109947155244277</v>
+      </c>
+      <c r="E179" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>68</v>
+      </c>
+      <c r="B180" t="s">
+        <v>313</v>
+      </c>
+      <c r="C180" t="s">
+        <v>307</v>
+      </c>
+      <c r="D180">
+        <v>0.9431086429505524</v>
+      </c>
+      <c r="E180" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>68</v>
+      </c>
+      <c r="B181" t="s">
+        <v>314</v>
+      </c>
+      <c r="C181" t="s">
+        <v>307</v>
+      </c>
+      <c r="D181">
+        <v>0.2799653465082028</v>
+      </c>
+      <c r="E181" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>69</v>
+      </c>
+      <c r="B182" t="s">
+        <v>312</v>
+      </c>
+      <c r="C182" t="s">
+        <v>307</v>
+      </c>
+      <c r="D182">
+        <v>0.9749195618217813</v>
+      </c>
+      <c r="E182" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>69</v>
+      </c>
+      <c r="B183" t="s">
+        <v>313</v>
+      </c>
+      <c r="C183" t="s">
+        <v>307</v>
+      </c>
+      <c r="D183">
+        <v>0.9749195618217813</v>
+      </c>
+      <c r="E183" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>69</v>
+      </c>
+      <c r="B184" t="s">
+        <v>314</v>
+      </c>
+      <c r="C184" t="s">
+        <v>307</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+      <c r="E184" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>70</v>
+      </c>
+      <c r="B185" t="s">
+        <v>312</v>
+      </c>
+      <c r="C185" t="s">
+        <v>307</v>
+      </c>
+      <c r="D185">
+        <v>0.5725089577171791</v>
+      </c>
+      <c r="E185" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>70</v>
+      </c>
+      <c r="B186" t="s">
+        <v>313</v>
+      </c>
+      <c r="C186" t="s">
+        <v>307</v>
+      </c>
+      <c r="D186">
+        <v>0.9312521042437503</v>
+      </c>
+      <c r="E186" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>70</v>
+      </c>
+      <c r="B187" t="s">
+        <v>314</v>
+      </c>
+      <c r="C187" t="s">
+        <v>307</v>
+      </c>
+      <c r="D187">
+        <v>0.39084911080187845</v>
+      </c>
+      <c r="E187" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>71</v>
+      </c>
+      <c r="B188" t="s">
+        <v>312</v>
+      </c>
+      <c r="C188" t="s">
+        <v>307</v>
+      </c>
+      <c r="D188">
+        <v>0.9998597978081878</v>
+      </c>
+      <c r="E188" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>71</v>
+      </c>
+      <c r="B189" t="s">
+        <v>313</v>
+      </c>
+      <c r="C189" t="s">
+        <v>307</v>
+      </c>
+      <c r="D189">
+        <v>0.9766399637650733</v>
+      </c>
+      <c r="E189" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>71</v>
+      </c>
+      <c r="B190" t="s">
+        <v>314</v>
+      </c>
+      <c r="C190" t="s">
+        <v>307</v>
+      </c>
+      <c r="D190">
+        <v>0.9729760240785255</v>
+      </c>
+      <c r="E190" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>72</v>
+      </c>
+      <c r="B191" t="s">
+        <v>312</v>
+      </c>
+      <c r="C191" t="s">
+        <v>307</v>
+      </c>
+      <c r="D191">
+        <v>0.9851476950492858</v>
+      </c>
+      <c r="E191" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>72</v>
+      </c>
+      <c r="B192" t="s">
+        <v>313</v>
+      </c>
+      <c r="C192" t="s">
+        <v>307</v>
+      </c>
+      <c r="D192">
+        <v>0.9851476950492862</v>
+      </c>
+      <c r="E192" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>72</v>
+      </c>
+      <c r="B193" t="s">
+        <v>314</v>
+      </c>
+      <c r="C193" t="s">
+        <v>307</v>
+      </c>
+      <c r="D193">
+        <v>1</v>
+      </c>
+      <c r="E193" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>73</v>
+      </c>
+      <c r="B194" t="s">
+        <v>312</v>
+      </c>
+      <c r="C194" t="s">
+        <v>307</v>
+      </c>
+      <c r="D194">
+        <v>0.9595719790600198</v>
+      </c>
+      <c r="E194" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>73</v>
+      </c>
+      <c r="B195" t="s">
+        <v>313</v>
+      </c>
+      <c r="C195" t="s">
+        <v>307</v>
+      </c>
+      <c r="D195">
+        <v>0.9595719790600198</v>
+      </c>
+      <c r="E195" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>73</v>
+      </c>
+      <c r="B196" t="s">
+        <v>314</v>
+      </c>
+      <c r="C196" t="s">
+        <v>307</v>
+      </c>
+      <c r="D196">
+        <v>1</v>
+      </c>
+      <c r="E196" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>74</v>
+      </c>
+      <c r="B197" t="s">
+        <v>312</v>
+      </c>
+      <c r="C197" t="s">
+        <v>307</v>
+      </c>
+      <c r="D197">
+        <v>0.9816369811944125</v>
+      </c>
+      <c r="E197" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>74</v>
+      </c>
+      <c r="B198" t="s">
+        <v>313</v>
+      </c>
+      <c r="C198" t="s">
+        <v>307</v>
+      </c>
+      <c r="D198">
+        <v>0.7625292384897487</v>
+      </c>
+      <c r="E198" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>74</v>
+      </c>
+      <c r="B199" t="s">
+        <v>314</v>
+      </c>
+      <c r="C199" t="s">
+        <v>307</v>
+      </c>
+      <c r="D199">
+        <v>0.6591254955004251</v>
+      </c>
+      <c r="E199" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>75</v>
+      </c>
+      <c r="B200" t="s">
+        <v>312</v>
+      </c>
+      <c r="C200" t="s">
+        <v>307</v>
+      </c>
+      <c r="D200">
+        <v>0.9246605216797662</v>
+      </c>
+      <c r="E200" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>75</v>
+      </c>
+      <c r="B201" t="s">
+        <v>313</v>
+      </c>
+      <c r="C201" t="s">
+        <v>307</v>
+      </c>
+      <c r="D201">
+        <v>0.9246605216797656</v>
+      </c>
+      <c r="E201" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" t="s">
+        <v>75</v>
+      </c>
+      <c r="B202" t="s">
+        <v>314</v>
+      </c>
+      <c r="C202" t="s">
+        <v>307</v>
+      </c>
+      <c r="D202">
+        <v>0.7397523980283058</v>
+      </c>
+      <c r="E202" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" t="s">
+        <v>76</v>
+      </c>
+      <c r="B203" t="s">
+        <v>312</v>
+      </c>
+      <c r="C203" t="s">
+        <v>307</v>
+      </c>
+      <c r="D203">
+        <v>0.9962775421314182</v>
+      </c>
+      <c r="E203" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" t="s">
+        <v>76</v>
+      </c>
+      <c r="B204" t="s">
+        <v>313</v>
+      </c>
+      <c r="C204" t="s">
+        <v>307</v>
+      </c>
+      <c r="D204">
+        <v>0.7845081779459584</v>
+      </c>
+      <c r="E204" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" t="s">
+        <v>76</v>
+      </c>
+      <c r="B205" t="s">
+        <v>314</v>
+      </c>
+      <c r="C205" t="s">
+        <v>307</v>
+      </c>
+      <c r="D205">
+        <v>0.7392758779029651</v>
+      </c>
+      <c r="E205" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" t="s">
+        <v>77</v>
+      </c>
+      <c r="B206" t="s">
+        <v>312</v>
+      </c>
+      <c r="C206" t="s">
+        <v>307</v>
+      </c>
+      <c r="D206">
+        <v>0.9945162651530931</v>
+      </c>
+      <c r="E206" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" t="s">
+        <v>77</v>
+      </c>
+      <c r="B207" t="s">
+        <v>313</v>
+      </c>
+      <c r="C207" t="s">
+        <v>307</v>
+      </c>
+      <c r="D207">
+        <v>0.8282377197532877</v>
+      </c>
+      <c r="E207" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" t="s">
+        <v>77</v>
+      </c>
+      <c r="B208" t="s">
+        <v>314</v>
+      </c>
+      <c r="C208" t="s">
+        <v>307</v>
+      </c>
+      <c r="D208">
+        <v>0.876608131108941</v>
+      </c>
+      <c r="E208" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" t="s">
+        <v>78</v>
+      </c>
+      <c r="B209" t="s">
+        <v>312</v>
+      </c>
+      <c r="C209" t="s">
+        <v>307</v>
+      </c>
+      <c r="D209">
+        <v>0.9959359583106772</v>
+      </c>
+      <c r="E209" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" t="s">
+        <v>78</v>
+      </c>
+      <c r="B210" t="s">
+        <v>313</v>
+      </c>
+      <c r="C210" t="s">
+        <v>307</v>
+      </c>
+      <c r="D210">
+        <v>0.7855996334875996</v>
+      </c>
+      <c r="E210" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" t="s">
+        <v>78</v>
+      </c>
+      <c r="B211" t="s">
+        <v>314</v>
+      </c>
+      <c r="C211" t="s">
+        <v>307</v>
+      </c>
+      <c r="D211">
+        <v>0.7383390684528308</v>
+      </c>
+      <c r="E211" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5532,12 +9152,12 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B2">
         <v>9</v>
@@ -5545,7 +9165,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -5553,7 +9173,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -5561,7 +9181,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B5">
         <v>73</v>
@@ -5569,12 +9189,12 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -5582,36 +9202,36 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B9" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B11" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B14">
         <v>70</v>
@@ -5619,20 +9239,20 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B17">
-        <v>0.12397393947407208</v>
+        <v>0.12397393947407209</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B18">
         <v>0.5861770597728554</v>
@@ -5640,7 +9260,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -5648,18 +9268,18 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B20" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B21">
-        <v>106</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/src-tauri/tests/fixtures/e2e_expected_output.xlsx
+++ b/src-tauri/tests/fixtures/e2e_expected_output.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="351">
   <si>
     <t>kg</t>
   </si>
@@ -995,6 +995,54 @@
   </si>
   <si>
     <t>组 3 配置</t>
+  </si>
+  <si>
+    <t>分组方法与可追溯性</t>
+  </si>
+  <si>
+    <t>应用场景</t>
+  </si>
+  <si>
+    <t>探索性 / 非 GLP 实验</t>
+  </si>
+  <si>
+    <t>分组方式</t>
+  </si>
+  <si>
+    <t>统计均衡优化</t>
+  </si>
+  <si>
+    <t>分组原理</t>
+  </si>
+  <si>
+    <t>按性别分层 + 统计均衡优化（择优搜索式分配，非随机）</t>
+  </si>
+  <si>
+    <t>分层变量</t>
+  </si>
+  <si>
+    <t>随机种子</t>
+  </si>
+  <si>
+    <t>不适用</t>
+  </si>
+  <si>
+    <t>随机数算法</t>
+  </si>
+  <si>
+    <t>抽样次数</t>
+  </si>
+  <si>
+    <t>输入指纹</t>
+  </si>
+  <si>
+    <t>c3cdeb15caace00d</t>
+  </si>
+  <si>
+    <t>引擎版本</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>统计配置</t>
@@ -9143,7 +9191,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -9233,53 +9281,130 @@
       <c r="A14" t="s">
         <v>327</v>
       </c>
-      <c r="B14">
-        <v>70</v>
+      <c r="B14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B15" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>328</v>
+      <c r="A16" t="s">
+        <v>331</v>
+      </c>
+      <c r="B16" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>329</v>
-      </c>
-      <c r="B17">
-        <v>0.12397393947407209</v>
+        <v>333</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>330</v>
-      </c>
-      <c r="B18">
-        <v>0.5861770597728554</v>
+        <v>334</v>
+      </c>
+      <c r="B18" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>331</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
+        <v>336</v>
+      </c>
+      <c r="B19" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B20" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>334</v>
-      </c>
-      <c r="B21">
-        <v>23</v>
+        <v>338</v>
+      </c>
+      <c r="B21" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>340</v>
+      </c>
+      <c r="B22" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>343</v>
+      </c>
+      <c r="B25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>345</v>
+      </c>
+      <c r="B28">
+        <v>0.12397393947407209</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29">
+        <v>0.5861770597728554</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>348</v>
+      </c>
+      <c r="B31" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>350</v>
+      </c>
+      <c r="B32">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
